--- a/sheets/조재수대금교본/검수/장녹수.xlsx
+++ b/sheets/조재수대금교본/검수/장녹수.xlsx
@@ -3582,34 +3582,33 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳⌝∽
-㳞է</t>
+          <t xml:space="preserve">湳
+㳞</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-汰⌝</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-ㄴ</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
@@ -3632,7 +3631,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∽</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3644,7 +3643,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -3668,7 +3667,7 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
@@ -3695,7 +3694,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-И汰</t>
+汰</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3707,8 +3706,7 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3722,54 +3720,32 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="21"/>
       <c r="S6" s="22"/>
@@ -3778,7 +3754,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋∽
+          <t xml:space="preserve">湳淋
 㳞淋</t>
         </is>
       </c>
@@ -3791,22 +3767,21 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝∽
+          <t xml:space="preserve">南
 仲南</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-⌝</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -3818,22 +3793,21 @@
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林∽
+          <t xml:space="preserve">南林
 仲林</t>
         </is>
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-⌝</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南⌝</t>
+南</t>
         </is>
       </c>
       <c r="S7" s="23"/>
@@ -3854,7 +3828,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -3901,8 +3875,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -3927,53 +3900,23 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-⌝
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="23"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
     <row r="11" ht="96.05" customHeight="true">
@@ -3987,7 +3930,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林∽
+          <t xml:space="preserve">南林
 仲林</t>
         </is>
       </c>
@@ -4001,8 +3944,7 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-⌝</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -4015,29 +3957,27 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳⌝∽
-㳞է</t>
+          <t xml:space="preserve">湳
+㳞</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林⌝</t>
+林</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ㄴ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -4072,7 +4012,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4084,7 +4024,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4111,8 +4051,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -4120,8 +4059,7 @@
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="23"/>
@@ -4137,47 +4075,26 @@
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="S14" s="24"/>

--- a/sheets/조재수대금교본/검수/장녹수.xlsx
+++ b/sheets/조재수대금교본/검수/장녹수.xlsx
@@ -3582,33 +3582,34 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-㳞</t>
+          <t xml:space="preserve">湳⌝∽
+㳞է</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㳞ʒ
+汰⌝</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃</t>
+          <t xml:space="preserve">黃
+ㄴ</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -3631,7 +3632,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∽</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3643,7 +3644,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -3667,7 +3668,7 @@
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 –</t>
         </is>
       </c>
@@ -3694,7 +3695,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
+И汰</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3706,7 +3707,8 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3741,7 +3743,7 @@
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -3754,7 +3756,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳淋
+          <t xml:space="preserve">湳淋∽
 㳞淋</t>
         </is>
       </c>
@@ -3767,21 +3769,22 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝∽
 仲南</t>
         </is>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳
+⌝</t>
         </is>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -3793,21 +3796,22 @@
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林
+          <t xml:space="preserve">南林∽
 仲林</t>
         </is>
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+⌝</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南</t>
+南⌝</t>
         </is>
       </c>
       <c r="S7" s="23"/>
@@ -3828,7 +3832,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林∽</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -3875,7 +3879,8 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -3900,7 +3905,8 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+⌝</t>
         </is>
       </c>
       <c r="E10" s="23"/>
@@ -3930,7 +3936,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林
+          <t xml:space="preserve">南林∽
 仲林</t>
         </is>
       </c>
@@ -3944,7 +3950,8 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋
+⌝</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -3957,27 +3964,29 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-㳞</t>
+          <t xml:space="preserve">湳⌝∽
+㳞է</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ㄴ</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+林⌝</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ㄴ</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -4012,7 +4021,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4024,7 +4033,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太∽</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4051,7 +4060,8 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -4059,7 +4069,8 @@
       <c r="Q13" s="23"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="S13" s="23"/>
@@ -4086,7 +4097,7 @@
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/장녹수.xlsx
+++ b/sheets/조재수대금교본/검수/장녹수.xlsx
@@ -3511,30 +3511,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="124.21" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="124.21" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="124.21" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="124.21" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="124.21" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="124.21" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="124.21" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3899,7 +3899,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="124.21" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3925,7 +3925,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="124.21" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="124.21" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="124.21" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="124.21" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4116,6 +4116,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>